--- a/survey_templates/050_mba_qualifying_survey--survey_templates.xlsx
+++ b/survey_templates/050_mba_qualifying_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="31" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -543,7 +543,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mba_qualifying_survey_page_1</t>
+          <t>mba_qualifying_survey_page_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mba_qualifying_survey_page_2</t>
+          <t>mba_qualifying_survey_page_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -574,14 +574,10 @@
           <t>What is your current annual income</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Enter a number</t>
-        </is>
-      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -593,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mba_qualifying_survey_page_3</t>
+          <t>mba_qualifying_survey_page_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>What is your current annual income (if employed)</t>
+          <t>How many years do you have work experience</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -616,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mba_qualifying_survey_page_4</t>
+          <t>mba_qualifying_survey_page_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>What is your highest level of education</t>
+          <t>Do you have any prior experience with a professional certification</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -634,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mba_qualifying_survey_page_5</t>
+          <t>mba_qualifying_survey_page_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>How many years do you have work experience</t>
+          <t>Have you taken the GMAT or GRE</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -657,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>mba_qualifying_survey_page_6</t>
+          <t>mba_qualifying_survey_page_7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>What is your current occupation</t>
+          <t>What was your GMAT or GRE score</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -685,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>mba_qualifying_survey_page_7</t>
+          <t>mba_qualifying_survey_page_8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>What is your current location</t>
+          <t>Do you have any prior experience of business administration</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -703,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>mba_qualifying_survey_page_8</t>
+          <t>mba_qualifying_survey_page_9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>What is your highest degree level</t>
+          <t>What is your annual income</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -726,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>mba_qualifying_survey_page_9</t>
+          <t>mba_qualifying_survey_page_10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>What is your current annual income</t>
+          <t>Do you have an MBA degree</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -749,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>mba_qualifying_survey_page_10</t>
+          <t>mba_qualifying_survey_page_11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>How many years do you have work experience in a management role</t>
+          <t>Have you taken any other entrance exams</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -772,24 +768,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>mba_qualifying_survey_page_11</t>
+          <t>mba_qualifying_survey_page_12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>What is your current annual income (if employed)</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Enter a number</t>
-        </is>
-      </c>
+          <t>What is your current location</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>yes</t>
@@ -804,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>mba_qualifying_survey_page_12</t>
+          <t>mba_qualifying_survey_page_13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Do you have any prior experience of a professional certification</t>
+          <t>Mba Qualifying Survey Page 13</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -822,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>mba_qualifying_survey_page_13</t>
+          <t>mba_qualifying_survey_page_14</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>How many years do you have experience with a professional certification</t>
+          <t>Mba Qualifying Survey Page 14</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -845,24 +837,20 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>mba_qualifying_survey_page_14</t>
+          <t>mba_qualifying_survey_page_15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>What is your current annual income</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Enter a number</t>
-        </is>
-      </c>
+          <t>Mba Qualifying Survey Page 15</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>yes</t>
@@ -872,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>mba_qualifying_survey_page_15</t>
+          <t>mba_qualifying_survey_page_16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Do you have an MBA degree</t>
+          <t>How many years do you have experience with a professional certification</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -895,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>mba_qualifying_survey_page_16</t>
+          <t>mba_qualifying_survey_page_17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>What is your highest degree level</t>
+          <t>Mba Qualifying Survey Page 17</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -918,182 +906,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>mba_qualifying_survey_page_17</t>
+          <t>mba_qualifying_survey_page_18</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>What is your annual income</t>
+          <t>Have you had any prior experience in business administration</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>mba_qualifying_survey_page_18</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Have you taken the GMAT or GRE</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>mba_qualifying_survey_page_19</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>What was your GMAT or GRE score</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>mba_qualifying_survey_page_20</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Have you taken any other entrance exams</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>mba_qualifying_survey_page_21</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>What is your current location</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>mba_qualifying_survey_page_22</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Do you have any prior experience in any of the areas of business administration</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>mba_qualifying_survey_page_23</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>What is your annual income</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>mba_qualifying_survey_page_24</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Do you have any prior experience of a professional certification</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -1110,7 +937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -1206,7 +1033,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>mba_qualifying_survey_page_1_choices</t>
+          <t>mba_qualifying_survey_page_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1223,7 +1050,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mba_qualifying_survey_page_1_choices</t>
+          <t>mba_qualifying_survey_page_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1240,68 +1067,68 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>mba_qualifying_survey_page_4_choices</t>
+          <t>mba_qualifying_survey_page_5_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>bachelors_degree</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bachelors degree</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mba_qualifying_survey_page_4_choices</t>
+          <t>mba_qualifying_survey_page_5_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>masters_degree</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Masters degree</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>mba_qualifying_survey_page_4_choices</t>
+          <t>mba_qualifying_survey_page_5_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>doctorate_degree</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Doctorate degree</t>
+          <t>unknown</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mba_qualifying_survey_page_4_choices</t>
+          <t>mba_qualifying_survey_page_6_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1313,131 +1140,131 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>mba_qualifying_survey_page_6_choices</t>
+          <t>mba_qualifying_survey_page_8_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>mba_qualifying_survey_page_7_choices</t>
+          <t>mba_qualifying_survey_page_8_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>mba_qualifying_survey_page_7_choices</t>
+          <t>mba_qualifying_survey_page_10_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>mba_qualifying_survey_page_8_choices</t>
+          <t>mba_qualifying_survey_page_10_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>bachelors_degree</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bachelors degree</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>mba_qualifying_survey_page_8_choices</t>
+          <t>mba_qualifying_survey_page_11_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>masters_degree</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Masters degree</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>mba_qualifying_survey_page_8_choices</t>
+          <t>mba_qualifying_survey_page_11_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>doctorate_degree</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Doctorate degree</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>mba_qualifying_survey_page_8_choices</t>
+          <t>mba_qualifying_survey_page_12_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1449,46 +1276,46 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>mba_qualifying_survey_page_12_choices</t>
+          <t>mba_qualifying_survey_page_13_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>bachelors_degree</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Bachelors degree</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>mba_qualifying_survey_page_12_choices</t>
+          <t>mba_qualifying_survey_page_13_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>masters_degree</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Masters degree</t>
         </is>
       </c>
     </row>
@@ -1500,12 +1327,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>doctorate_degree</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Doctorate degree</t>
         </is>
       </c>
     </row>
@@ -1517,12 +1344,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1563,236 +1390,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>mba_qualifying_survey_page_16_choices</t>
+          <t>mba_qualifying_survey_page_18_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>bachelors_degree</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bachelors degree</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>mba_qualifying_survey_page_16_choices</t>
+          <t>mba_qualifying_survey_page_18_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>masters_degree</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
-        <is>
-          <t>Masters degree</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>mba_qualifying_survey_page_16_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>doctorate_degree</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Doctorate degree</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>mba_qualifying_survey_page_16_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>mba_qualifying_survey_page_18_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>mba_qualifying_survey_page_18_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>mba_qualifying_survey_page_20_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>mba_qualifying_survey_page_20_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>mba_qualifying_survey_page_21_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>mba_qualifying_survey_page_21_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>mba_qualifying_survey_page_22_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>mba_qualifying_survey_page_22_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>mba_qualifying_survey_page_24_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>mba_qualifying_survey_page_24_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
         <is>
           <t>no</t>
         </is>
